--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_7sep26_Mon.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_7sep26_Mon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3697612-AAFF-427D-9B80-D7273D393B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60620D13-6B2C-4282-B580-4924A1AF12BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
